--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_28-05-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_28-05-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Celotex_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ED13675-A190-4389-969E-69F8632C4B1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC9F28F9-35FB-4B6A-BE3C-38B5A8DE3876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4125" yWindow="1080" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30255" yWindow="3075" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="394">
   <si>
     <t>SKU</t>
   </si>
@@ -850,9 +850,6 @@
     <t>£54.75</t>
   </si>
   <si>
-    <t>£302.08</t>
-  </si>
-  <si>
     <t>£58.13</t>
   </si>
   <si>
@@ -1120,9 +1117,6 @@
     <t>£2007.52</t>
   </si>
   <si>
-    <t>£128.48</t>
-  </si>
-  <si>
     <t>£1898.88</t>
   </si>
   <si>
@@ -1159,9 +1153,6 @@
     <t>£1870.08</t>
   </si>
   <si>
-    <t>£177.92</t>
-  </si>
-  <si>
     <t>£2114.24</t>
   </si>
   <si>
@@ -1195,9 +1186,6 @@
     <t>£1984.64</t>
   </si>
   <si>
-    <t>£199.16</t>
-  </si>
-  <si>
     <t>£2152.0</t>
   </si>
   <si>
@@ -1205,6 +1193,15 @@
   </si>
   <si>
     <t>£2265.12</t>
+  </si>
+  <si>
+    <t>£2055.68</t>
+  </si>
+  <si>
+    <t>£2846.72</t>
+  </si>
+  <si>
+    <t>£3186.56</t>
   </si>
 </sst>
 </file>
@@ -2660,222 +2657,222 @@
         <v>275</v>
       </c>
       <c r="I20" t="s">
+        <v>206</v>
+      </c>
+      <c r="J20" t="s">
         <v>276</v>
       </c>
-      <c r="J20" t="s">
+      <c r="K20" t="s">
         <v>277</v>
-      </c>
-      <c r="K20" t="s">
-        <v>278</v>
       </c>
       <c r="L20" t="s">
         <v>27</v>
       </c>
       <c r="M20" t="s">
+        <v>278</v>
+      </c>
+      <c r="N20" t="s">
         <v>279</v>
       </c>
-      <c r="N20" t="s">
+      <c r="O20" t="s">
         <v>280</v>
       </c>
-      <c r="O20" t="s">
+      <c r="P20" t="s">
         <v>281</v>
       </c>
-      <c r="P20" t="s">
+      <c r="Q20" t="s">
         <v>282</v>
       </c>
-      <c r="Q20" t="s">
+      <c r="R20" t="s">
         <v>283</v>
-      </c>
-      <c r="R20" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>284</v>
+      </c>
+      <c r="B21" t="s">
         <v>285</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>286</v>
       </c>
-      <c r="C21" t="s">
-        <v>287</v>
-      </c>
       <c r="D21" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E21" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F21" t="s">
         <v>188</v>
       </c>
       <c r="G21" t="s">
+        <v>287</v>
+      </c>
+      <c r="H21" t="s">
         <v>288</v>
       </c>
-      <c r="H21" t="s">
+      <c r="I21" t="s">
         <v>289</v>
       </c>
-      <c r="I21" t="s">
+      <c r="J21" t="s">
         <v>290</v>
       </c>
-      <c r="J21" t="s">
+      <c r="K21" t="s">
         <v>291</v>
-      </c>
-      <c r="K21" t="s">
-        <v>292</v>
       </c>
       <c r="L21" t="s">
         <v>27</v>
       </c>
       <c r="M21" t="s">
+        <v>292</v>
+      </c>
+      <c r="N21" t="s">
         <v>293</v>
       </c>
-      <c r="N21" t="s">
+      <c r="O21" t="s">
         <v>294</v>
       </c>
-      <c r="O21" t="s">
+      <c r="P21" t="s">
         <v>295</v>
       </c>
-      <c r="P21" t="s">
+      <c r="Q21" t="s">
         <v>296</v>
       </c>
-      <c r="Q21" t="s">
+      <c r="R21" t="s">
         <v>297</v>
-      </c>
-      <c r="R21" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>298</v>
+      </c>
+      <c r="B22" t="s">
         <v>299</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>300</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
+        <v>300</v>
+      </c>
+      <c r="E22" t="s">
+        <v>300</v>
+      </c>
+      <c r="F22" t="s">
         <v>301</v>
       </c>
-      <c r="D22" t="s">
-        <v>301</v>
-      </c>
-      <c r="E22" t="s">
-        <v>301</v>
-      </c>
-      <c r="F22" t="s">
+      <c r="G22" t="s">
         <v>302</v>
       </c>
-      <c r="G22" t="s">
+      <c r="H22" t="s">
         <v>303</v>
       </c>
-      <c r="H22" t="s">
+      <c r="I22" t="s">
         <v>304</v>
       </c>
-      <c r="I22" t="s">
+      <c r="J22" t="s">
         <v>305</v>
       </c>
-      <c r="J22" t="s">
+      <c r="K22" t="s">
         <v>306</v>
-      </c>
-      <c r="K22" t="s">
-        <v>307</v>
       </c>
       <c r="L22" t="s">
         <v>27</v>
       </c>
       <c r="M22" t="s">
+        <v>307</v>
+      </c>
+      <c r="N22" t="s">
         <v>308</v>
-      </c>
-      <c r="N22" t="s">
-        <v>309</v>
       </c>
       <c r="O22" t="s">
         <v>213</v>
       </c>
       <c r="P22" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="Q22" t="s">
         <v>202</v>
       </c>
       <c r="R22" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>311</v>
+      </c>
+      <c r="B23" t="s">
         <v>312</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>313</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
+        <v>313</v>
+      </c>
+      <c r="E23" t="s">
+        <v>313</v>
+      </c>
+      <c r="F23" t="s">
         <v>314</v>
-      </c>
-      <c r="D23" t="s">
-        <v>314</v>
-      </c>
-      <c r="E23" t="s">
-        <v>314</v>
-      </c>
-      <c r="F23" t="s">
-        <v>315</v>
       </c>
       <c r="G23" t="s">
         <v>163</v>
       </c>
       <c r="H23" t="s">
+        <v>315</v>
+      </c>
+      <c r="I23" t="s">
         <v>316</v>
       </c>
-      <c r="I23" t="s">
+      <c r="J23" t="s">
         <v>317</v>
       </c>
-      <c r="J23" t="s">
+      <c r="K23" t="s">
         <v>318</v>
-      </c>
-      <c r="K23" t="s">
-        <v>319</v>
       </c>
       <c r="L23" t="s">
         <v>27</v>
       </c>
       <c r="M23" t="s">
+        <v>319</v>
+      </c>
+      <c r="N23" t="s">
         <v>320</v>
       </c>
-      <c r="N23" t="s">
+      <c r="O23" t="s">
         <v>321</v>
       </c>
-      <c r="O23" t="s">
+      <c r="P23" t="s">
         <v>322</v>
       </c>
-      <c r="P23" t="s">
+      <c r="Q23" t="s">
         <v>323</v>
       </c>
-      <c r="Q23" t="s">
+      <c r="R23" t="s">
         <v>324</v>
-      </c>
-      <c r="R23" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>325</v>
+      </c>
+      <c r="B24" t="s">
         <v>326</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>327</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
+        <v>327</v>
+      </c>
+      <c r="E24" t="s">
+        <v>327</v>
+      </c>
+      <c r="F24" t="s">
         <v>328</v>
-      </c>
-      <c r="D24" t="s">
-        <v>328</v>
-      </c>
-      <c r="E24" t="s">
-        <v>328</v>
-      </c>
-      <c r="F24" t="s">
-        <v>329</v>
       </c>
       <c r="G24" t="s">
         <v>163</v>
@@ -2884,51 +2881,51 @@
         <v>223</v>
       </c>
       <c r="I24" t="s">
+        <v>329</v>
+      </c>
+      <c r="J24" t="s">
         <v>330</v>
       </c>
-      <c r="J24" t="s">
+      <c r="K24" t="s">
         <v>331</v>
-      </c>
-      <c r="K24" t="s">
-        <v>332</v>
       </c>
       <c r="L24" t="s">
         <v>27</v>
       </c>
       <c r="M24" t="s">
+        <v>332</v>
+      </c>
+      <c r="N24" t="s">
         <v>333</v>
       </c>
-      <c r="N24" t="s">
+      <c r="O24" t="s">
         <v>334</v>
       </c>
-      <c r="O24" t="s">
+      <c r="P24" t="s">
         <v>335</v>
       </c>
-      <c r="P24" t="s">
+      <c r="Q24" t="s">
         <v>336</v>
       </c>
-      <c r="Q24" t="s">
+      <c r="R24" t="s">
         <v>337</v>
-      </c>
-      <c r="R24" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>338</v>
+      </c>
+      <c r="B25" t="s">
         <v>339</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>340</v>
       </c>
-      <c r="C25" t="s">
-        <v>341</v>
-      </c>
       <c r="D25" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E25" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F25" t="s">
         <v>163</v>
@@ -2943,7 +2940,7 @@
         <v>163</v>
       </c>
       <c r="J25" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="K25" t="s">
         <v>163</v>
@@ -2952,13 +2949,13 @@
         <v>163</v>
       </c>
       <c r="M25" t="s">
+        <v>342</v>
+      </c>
+      <c r="N25" t="s">
         <v>343</v>
       </c>
-      <c r="N25" t="s">
+      <c r="O25" t="s">
         <v>344</v>
-      </c>
-      <c r="O25" t="s">
-        <v>345</v>
       </c>
       <c r="P25" t="s">
         <v>163</v>
@@ -2972,226 +2969,226 @@
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>345</v>
+      </c>
+      <c r="B26" t="s">
         <v>346</v>
       </c>
-      <c r="B26" t="s">
-        <v>347</v>
-      </c>
       <c r="C26" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D26" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E26" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F26" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G26" t="s">
         <v>163</v>
       </c>
       <c r="H26" t="s">
+        <v>347</v>
+      </c>
+      <c r="I26" t="s">
         <v>348</v>
       </c>
-      <c r="I26" t="s">
+      <c r="J26" t="s">
         <v>349</v>
       </c>
-      <c r="J26" t="s">
+      <c r="K26" t="s">
         <v>350</v>
-      </c>
-      <c r="K26" t="s">
-        <v>351</v>
       </c>
       <c r="L26" t="s">
         <v>27</v>
       </c>
       <c r="M26" t="s">
+        <v>351</v>
+      </c>
+      <c r="N26" t="s">
         <v>352</v>
       </c>
-      <c r="N26" t="s">
+      <c r="O26" t="s">
         <v>353</v>
       </c>
-      <c r="O26" t="s">
+      <c r="P26" t="s">
         <v>354</v>
       </c>
-      <c r="P26" t="s">
+      <c r="Q26" t="s">
         <v>355</v>
       </c>
-      <c r="Q26" t="s">
+      <c r="R26" t="s">
         <v>356</v>
-      </c>
-      <c r="R26" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>357</v>
+      </c>
+      <c r="B27" t="s">
         <v>358</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
         <v>359</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
+        <v>359</v>
+      </c>
+      <c r="E27" t="s">
+        <v>359</v>
+      </c>
+      <c r="F27" t="s">
         <v>360</v>
-      </c>
-      <c r="D27" t="s">
-        <v>360</v>
-      </c>
-      <c r="E27" t="s">
-        <v>360</v>
-      </c>
-      <c r="F27" t="s">
-        <v>361</v>
       </c>
       <c r="G27" t="s">
         <v>163</v>
       </c>
       <c r="H27" t="s">
+        <v>361</v>
+      </c>
+      <c r="I27" t="s">
         <v>362</v>
-      </c>
-      <c r="I27" t="s">
-        <v>363</v>
       </c>
       <c r="J27" t="s">
         <v>163</v>
       </c>
       <c r="K27" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="L27" t="s">
         <v>27</v>
       </c>
       <c r="M27" t="s">
+        <v>364</v>
+      </c>
+      <c r="N27" t="s">
+        <v>391</v>
+      </c>
+      <c r="O27" t="s">
         <v>365</v>
       </c>
-      <c r="N27" t="s">
+      <c r="P27" t="s">
         <v>366</v>
       </c>
-      <c r="O27" t="s">
+      <c r="Q27" t="s">
         <v>367</v>
       </c>
-      <c r="P27" t="s">
+      <c r="R27" t="s">
         <v>368</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>369</v>
-      </c>
-      <c r="R27" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>369</v>
+      </c>
+      <c r="B28" t="s">
+        <v>370</v>
+      </c>
+      <c r="C28" t="s">
         <v>371</v>
       </c>
-      <c r="B28" t="s">
+      <c r="D28" t="s">
+        <v>371</v>
+      </c>
+      <c r="E28" t="s">
+        <v>371</v>
+      </c>
+      <c r="F28" t="s">
         <v>372</v>
-      </c>
-      <c r="C28" t="s">
-        <v>373</v>
-      </c>
-      <c r="D28" t="s">
-        <v>373</v>
-      </c>
-      <c r="E28" t="s">
-        <v>373</v>
-      </c>
-      <c r="F28" t="s">
-        <v>374</v>
       </c>
       <c r="G28" t="s">
         <v>163</v>
       </c>
       <c r="H28" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="I28" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="J28" t="s">
         <v>163</v>
       </c>
       <c r="K28" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="L28" t="s">
         <v>27</v>
       </c>
       <c r="M28" t="s">
+        <v>376</v>
+      </c>
+      <c r="N28" t="s">
+        <v>392</v>
+      </c>
+      <c r="O28" t="s">
+        <v>377</v>
+      </c>
+      <c r="P28" t="s">
         <v>378</v>
       </c>
-      <c r="N28" t="s">
+      <c r="Q28" t="s">
         <v>379</v>
       </c>
-      <c r="O28" t="s">
+      <c r="R28" t="s">
         <v>380</v>
-      </c>
-      <c r="P28" t="s">
-        <v>381</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>382</v>
-      </c>
-      <c r="R28" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B29" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="C29" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="D29" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="E29" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="F29" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="G29" t="s">
         <v>163</v>
       </c>
       <c r="H29" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="I29" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="J29" t="s">
         <v>163</v>
       </c>
       <c r="K29" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="L29" t="s">
         <v>163</v>
       </c>
       <c r="M29" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="N29" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="O29" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="P29" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="Q29" t="s">
         <v>163</v>
       </c>
       <c r="R29" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
     </row>
   </sheetData>
